--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260213_202620.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
